--- a/benchmark/generated_files/RISP-1_V_045.xlsx
+++ b/benchmark/generated_files/RISP-1_V_045.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A2:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -443,38 +443,31 @@
     <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Saldo iniziale: 6.668,99 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Filiale: SEDE CENTRALE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tipo conto: Conto risparmio</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Periodo: 01/01/2026 - 28/02/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Movimenti al 28/02/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Intestatario: Marco Rossi + Laura Bianchi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IBAN: IT33 D034 4001 6000 0000 0468 012</t>
+          <t>Divisa: EUR</t>
         </is>
       </c>
     </row>
@@ -488,14 +481,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Intestatario: Marco Rossi + Laura Bianchi</t>
+          <t>Saldo iniziale: 10.527,78 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Codice cliente: 381565</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Movimenti al 28/02/2026</t>
+          <t>Tipo conto: Conto risparmio</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IBAN: IT33 D034 4001 6000 0000 0468 012</t>
         </is>
       </c>
     </row>
@@ -528,10 +535,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
@@ -539,7 +546,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>-517.03</v>
+        <v>-595.65</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -549,10 +556,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
@@ -560,7 +567,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-520.3</v>
+        <v>-577.97</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -570,10 +577,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
@@ -581,7 +588,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-454.21</v>
+        <v>-538.27</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -591,10 +598,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -602,7 +609,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-535.7</v>
+        <v>-578.45</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -612,10 +619,10 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
@@ -623,7 +630,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>-574.52</v>
+        <v>-570.05</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -633,10 +640,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
@@ -644,7 +651,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-435.19</v>
+        <v>-522.4299999999999</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -654,10 +661,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
@@ -665,7 +672,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-436.1</v>
+        <v>-541.92</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -686,7 +693,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-526.74</v>
+        <v>-469.53</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -696,10 +703,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
@@ -707,7 +714,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-519.59</v>
+        <v>-473.92</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -717,10 +724,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
@@ -728,7 +735,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-408.23</v>
+        <v>-468.07</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -738,10 +745,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46037</v>
+        <v>46029</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
@@ -749,7 +756,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-555.37</v>
+        <v>-514.03</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -759,10 +766,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
@@ -770,7 +777,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-488.93</v>
+        <v>-503.02</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -780,10 +787,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46037</v>
+        <v>46029</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
@@ -791,7 +798,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-505.62</v>
+        <v>-472.58</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -801,10 +808,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46037</v>
+        <v>46032</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
@@ -812,7 +819,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-426.25</v>
+        <v>-428.31</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -822,10 +829,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46038</v>
+        <v>46032</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46039</v>
+        <v>46033</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
@@ -833,7 +840,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-500.8</v>
+        <v>-473.64</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -843,10 +850,10 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46038</v>
+        <v>46032</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46038</v>
+        <v>46032</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
@@ -854,7 +861,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-404.91</v>
+        <v>-568.37</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -864,10 +871,10 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46038</v>
+        <v>46032</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46039</v>
+        <v>46032</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
@@ -875,7 +882,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-591.27</v>
+        <v>-421.57</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -885,10 +892,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46039</v>
+        <v>46033</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46039</v>
+        <v>46034</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
@@ -896,7 +903,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-526.01</v>
+        <v>-487.2</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -906,10 +913,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46040</v>
+        <v>46034</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46041</v>
+        <v>46035</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
@@ -917,7 +924,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-580.7</v>
+        <v>-593.05</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -927,10 +934,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46044</v>
+        <v>46034</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46044</v>
+        <v>46034</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
@@ -938,7 +945,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-514.15</v>
+        <v>-457.34</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -948,18 +955,18 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46045</v>
+        <v>46035</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46046</v>
+        <v>46036</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
+          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q4 2025</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-540.45</v>
+        <v>27.07</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -969,10 +976,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46046</v>
+        <v>46037</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
@@ -980,7 +987,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-431.15</v>
+        <v>-501.21</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -990,18 +997,18 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46046</v>
+        <v>46037</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46046</v>
+        <v>46038</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q1 2026</t>
+          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>25.33</v>
+        <v>-443.74</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1011,10 +1018,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46046</v>
+        <v>46037</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46046</v>
+        <v>46037</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
@@ -1022,7 +1029,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>-574.89</v>
+        <v>-403.04</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -1032,10 +1039,10 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46049</v>
+        <v>46038</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46049</v>
+        <v>46039</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
@@ -1043,7 +1050,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-552.61</v>
+        <v>-538.72</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1053,10 +1060,10 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46052</v>
+        <v>46038</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46052</v>
+        <v>46038</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
@@ -1064,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-523.0700000000001</v>
+        <v>-456.31</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -1074,10 +1081,10 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46052</v>
+        <v>46040</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46052</v>
+        <v>46040</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
@@ -1085,7 +1092,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-485.88</v>
+        <v>-460.88</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1095,10 +1102,10 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46055</v>
+        <v>46040</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
@@ -1106,7 +1113,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>-593.5700000000001</v>
+        <v>-587.35</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1116,10 +1123,10 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46055</v>
+        <v>46041</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46056</v>
+        <v>46042</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
@@ -1127,7 +1134,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>-500.91</v>
+        <v>-498.02</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1137,10 +1144,10 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46056</v>
+        <v>46041</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46057</v>
+        <v>46041</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
@@ -1148,7 +1155,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>-447.09</v>
+        <v>-460.47</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1158,10 +1165,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46057</v>
+        <v>46041</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46057</v>
+        <v>46041</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
@@ -1169,7 +1176,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>-456.71</v>
+        <v>-492.99</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1179,10 +1186,10 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46057</v>
+        <v>46043</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46058</v>
+        <v>46043</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
@@ -1190,7 +1197,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>-571.8200000000001</v>
+        <v>-548.72</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -1200,10 +1207,10 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46057</v>
+        <v>46044</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46058</v>
+        <v>46044</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1218,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>-581.95</v>
+        <v>-498.37</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1221,10 +1228,10 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46058</v>
+        <v>46044</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46058</v>
+        <v>46045</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
@@ -1232,7 +1239,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>-558.4</v>
+        <v>-547.8</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -1242,10 +1249,10 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46058</v>
+        <v>46045</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46058</v>
+        <v>46046</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1260,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>-566.39</v>
+        <v>-534.37</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -1263,10 +1270,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46059</v>
+        <v>46046</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46060</v>
+        <v>46047</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
@@ -1274,7 +1281,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>-581.97</v>
+        <v>-466.95</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -1284,18 +1291,18 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46060</v>
+        <v>46046</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46060</v>
+        <v>46047</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q1 2026</t>
+          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>16.83</v>
+        <v>-467.23</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -1305,18 +1312,18 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46060</v>
+        <v>46047</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46060</v>
+        <v>46048</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
+          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q4 2025</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>-564.59</v>
+        <v>48.34</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -1326,18 +1333,18 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46060</v>
+        <v>46049</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46060</v>
+        <v>46049</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
+          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q4 2025</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>-432.51</v>
+        <v>48.85</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -1347,10 +1354,10 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46060</v>
+        <v>46049</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46061</v>
+        <v>46050</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
@@ -1358,7 +1365,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>-579.73</v>
+        <v>-510.27</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -1368,10 +1375,10 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46061</v>
+        <v>46049</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46062</v>
+        <v>46050</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
@@ -1379,7 +1386,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>-447.95</v>
+        <v>-515.9400000000001</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -1389,10 +1396,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46062</v>
+        <v>46053</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46063</v>
+        <v>46053</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
@@ -1400,7 +1407,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>-541.66</v>
+        <v>-442.87</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -1410,10 +1417,10 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
@@ -1421,7 +1428,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-574.7</v>
+        <v>-535.29</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -1431,10 +1438,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46062</v>
+        <v>46055</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
@@ -1442,7 +1449,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>-523.47</v>
+        <v>-521.75</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -1452,10 +1459,10 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46063</v>
+        <v>46055</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46064</v>
+        <v>46055</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
@@ -1463,7 +1470,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>-592.39</v>
+        <v>-468.55</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -1473,10 +1480,10 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46064</v>
+        <v>46056</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46064</v>
+        <v>46057</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
@@ -1484,7 +1491,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>-498.77</v>
+        <v>-441.05</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -1494,10 +1501,10 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46065</v>
+        <v>46056</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46065</v>
+        <v>46056</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
@@ -1505,7 +1512,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>-532.3</v>
+        <v>-589.47</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -1515,10 +1522,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46066</v>
+        <v>46056</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46066</v>
+        <v>46056</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
@@ -1526,7 +1533,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>-547.86</v>
+        <v>-583.37</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -1536,10 +1543,10 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46066</v>
+        <v>46058</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46066</v>
+        <v>46058</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
@@ -1547,7 +1554,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>-532.28</v>
+        <v>-477.65</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -1557,10 +1564,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46067</v>
+        <v>46059</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
@@ -1568,7 +1575,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>-596.4</v>
+        <v>-551.72</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -1578,10 +1585,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
@@ -1589,7 +1596,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-455.16</v>
+        <v>-532.63</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -1599,10 +1606,10 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46067</v>
+        <v>46060</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46068</v>
+        <v>46061</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
@@ -1610,7 +1617,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>-559.35</v>
+        <v>-583.27</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
@@ -1620,10 +1627,10 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46067</v>
+        <v>46062</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46068</v>
+        <v>46063</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1638,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>-481.45</v>
+        <v>-458.4</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -1641,10 +1648,10 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46067</v>
+        <v>46062</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46068</v>
+        <v>46063</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
@@ -1652,7 +1659,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>-595.8099999999999</v>
+        <v>-522.52</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -1662,10 +1669,10 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46068</v>
+        <v>46062</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46069</v>
+        <v>46063</v>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
@@ -1673,7 +1680,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>-587.0599999999999</v>
+        <v>-490.34</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -1683,18 +1690,18 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46069</v>
+        <v>46063</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46069</v>
+        <v>46063</v>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q4 2025</t>
+          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>17.71</v>
+        <v>-530.11</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
@@ -1704,10 +1711,10 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46069</v>
+        <v>46063</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46069</v>
+        <v>46064</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
@@ -1715,7 +1722,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>-547.8200000000001</v>
+        <v>-428.11</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -1725,10 +1732,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46069</v>
+        <v>46063</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46070</v>
+        <v>46063</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
@@ -1736,7 +1743,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>-464.31</v>
+        <v>-568.2</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -1746,10 +1753,10 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46072</v>
+        <v>46064</v>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
@@ -1757,7 +1764,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>-469.77</v>
+        <v>-578.97</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -1767,10 +1774,10 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46072</v>
+        <v>46064</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46072</v>
+        <v>46065</v>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
@@ -1778,7 +1785,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-427.69</v>
+        <v>-597.8</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -1788,10 +1795,10 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46072</v>
+        <v>46064</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46073</v>
+        <v>46064</v>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
@@ -1799,7 +1806,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>-510.11</v>
+        <v>-543.8</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -1809,18 +1816,18 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46072</v>
+        <v>46065</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46072</v>
+        <v>46065</v>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
+          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q1 2026</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>-549.64</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
@@ -1830,10 +1837,10 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46072</v>
+        <v>46065</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46073</v>
+        <v>46065</v>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
@@ -1841,7 +1848,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>-512.22</v>
+        <v>-501.27</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -1851,10 +1858,10 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46073</v>
+        <v>46065</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46074</v>
+        <v>46066</v>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
@@ -1862,7 +1869,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>-460.77</v>
+        <v>-485.48</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -1872,18 +1879,18 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46074</v>
+        <v>46066</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46075</v>
+        <v>46066</v>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO INTERESSI MATURATI TRIMESTRE Q4 2025</t>
+          <t>GIROCONTO DA CC 0468012 A CC 0123456 PRELIEVO RISPARMIO</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>67.93000000000001</v>
+        <v>-524.89</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -1893,10 +1900,10 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46074</v>
+        <v>46066</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46074</v>
+        <v>46066</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1911,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>-534.11</v>
+        <v>-433.08</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
@@ -1914,10 +1921,10 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46076</v>
+        <v>46067</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46077</v>
+        <v>46067</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
@@ -1925,7 +1932,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>-479.26</v>
+        <v>-521.22</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -1935,10 +1942,10 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46077</v>
+        <v>46068</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46078</v>
+        <v>46068</v>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
@@ -1946,7 +1953,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-442.82</v>
+        <v>-414.99</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
@@ -1956,10 +1963,10 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46078</v>
+        <v>46068</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46078</v>
+        <v>46069</v>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
@@ -1967,7 +1974,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-583.6799999999999</v>
+        <v>-433.49</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -1977,10 +1984,10 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46078</v>
+        <v>46070</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46079</v>
+        <v>46071</v>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
@@ -1988,7 +1995,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>-415.02</v>
+        <v>-452.77</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -1998,10 +2005,10 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46078</v>
+        <v>46071</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46078</v>
+        <v>46071</v>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2016,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-413.32</v>
+        <v>-519.78</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -2019,10 +2026,10 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46080</v>
+        <v>46073</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46080</v>
+        <v>46074</v>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
@@ -2030,7 +2037,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-497.82</v>
+        <v>-465.31</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -2040,10 +2047,10 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46081</v>
+        <v>46075</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46082</v>
+        <v>46076</v>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
@@ -2051,7 +2058,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-538.79</v>
+        <v>-426.34</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -2061,10 +2068,10 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46081</v>
+        <v>46076</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46082</v>
+        <v>46076</v>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
@@ -2072,7 +2079,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>-434.46</v>
+        <v>-520.45</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -2082,10 +2089,10 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46081</v>
+        <v>46078</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46081</v>
+        <v>46078</v>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
@@ -2093,7 +2100,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-552.2</v>
+        <v>-598.87</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -2104,7 +2111,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Saldo finale: 24.102,89 EUR</t>
+          <t>Saldo finale: 25.913,42 EUR</t>
         </is>
       </c>
     </row>
